--- a/Exc2/FURPS_table.xlsx
+++ b/Exc2/FURPS_table.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="70">
   <si>
     <t>Код</t>
   </si>
@@ -203,6 +203,27 @@
   </si>
   <si>
     <t>Реализацию подтверждения операции через  СМС необходимо реализовать вне ядра АБС</t>
+  </si>
+  <si>
+    <t>F9</t>
+  </si>
+  <si>
+    <t>Сотрудник колл-центра должен обрабатывать заявки с сайта в системе колл-центра и отправлять их далее в АБС</t>
+  </si>
+  <si>
+    <t>Сайт должен работать без перезагрузки страницы, отклик по операциям менее 500 милликунд, начальная загрузка сайте должна занимать менее 5 секунд</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>Текущая платформа интернет-банка не совместима с Kafka</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>АБС поддерживает только вертикальное масштабирование</t>
   </si>
 </sst>
 </file>
@@ -277,7 +298,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -351,19 +372,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color theme="1"/>
@@ -389,7 +397,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -420,25 +428,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -665,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="12.75"/>
   <cols>
     <col min="2" max="2" width="6.85546875" customWidth="1"/>
@@ -690,10 +701,10 @@
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="16"/>
+      <c r="D4" s="17"/>
     </row>
     <row r="5" spans="2:6" ht="30" customHeight="1">
       <c r="B5" s="2" t="s">
@@ -711,7 +722,7 @@
       <c r="C6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="3"/>
     </row>
     <row r="7" spans="2:6" ht="54" customHeight="1">
       <c r="B7" s="2" t="s">
@@ -770,209 +781,238 @@
       </c>
       <c r="D12" s="8"/>
     </row>
-    <row r="13" spans="2:6" ht="30" customHeight="1">
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="2:6" ht="87.75" customHeight="1">
+      <c r="B13" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="15"/>
+    </row>
+    <row r="14" spans="2:6" ht="30" customHeight="1">
+      <c r="B14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C14" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="16"/>
-    </row>
-    <row r="14" spans="2:6" ht="66.75" customHeight="1">
-      <c r="B14" s="9" t="s">
+      <c r="D14" s="17"/>
+    </row>
+    <row r="15" spans="2:6" ht="66.75" customHeight="1">
+      <c r="B15" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C15" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="12"/>
-    </row>
-    <row r="15" spans="2:6" ht="77.25" customHeight="1">
-      <c r="B15" s="14" t="s">
+      <c r="D15" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="77.25" customHeight="1">
+      <c r="B16" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C16" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D16" s="12" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="30" customHeight="1">
-      <c r="B16" s="2" t="s">
+    <row r="17" spans="1:4" ht="30" customHeight="1">
+      <c r="B17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C17" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="18"/>
-    </row>
-    <row r="17" spans="1:4" ht="47.25" customHeight="1">
-      <c r="B17" s="9" t="s">
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4" ht="47.25" customHeight="1">
+      <c r="B18" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C18" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4" ht="87" customHeight="1">
-      <c r="B18" s="9" t="s">
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" spans="1:4" ht="87" customHeight="1">
+      <c r="B19" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C19" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="4"/>
-    </row>
-    <row r="19" spans="1:4" ht="30" customHeight="1">
-      <c r="B19" s="2" t="s">
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" spans="1:4" ht="30" customHeight="1">
+      <c r="B20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C20" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="16"/>
-    </row>
-    <row r="20" spans="1:4" ht="53.25" customHeight="1">
-      <c r="B20" s="9" t="s">
+      <c r="D20" s="17"/>
+    </row>
+    <row r="21" spans="1:4" ht="53.25" customHeight="1">
+      <c r="B21" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C21" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21" spans="1:4" ht="30" customHeight="1">
-      <c r="B21" s="5"/>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" spans="1:4" ht="30" customHeight="1">
+      <c r="B22" s="5"/>
+      <c r="C22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22" spans="1:4" ht="30" customHeight="1">
-      <c r="B22" s="2" t="s">
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="1:4" ht="30" customHeight="1">
+      <c r="B23" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C23" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="16"/>
-    </row>
-    <row r="23" spans="1:4" ht="30" customHeight="1">
-      <c r="B23" s="9" t="s">
+      <c r="D23" s="17"/>
+    </row>
+    <row r="24" spans="1:4" ht="30" customHeight="1">
+      <c r="B24" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C24" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" spans="1:4" ht="30" customHeight="1">
-      <c r="B24" s="5"/>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="1:4" ht="30" customHeight="1">
+      <c r="B25" s="5"/>
+      <c r="C25" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25" spans="1:4" ht="30" customHeight="1">
-      <c r="B25" s="2" t="s">
+      <c r="D25" s="4"/>
+    </row>
+    <row r="26" spans="1:4" ht="30" customHeight="1">
+      <c r="B26" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C26" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="16"/>
-    </row>
-    <row r="26" spans="1:4" ht="35.25" customHeight="1">
-      <c r="A26" s="6"/>
-      <c r="B26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27" spans="1:4" ht="66" customHeight="1">
+      <c r="D26" s="17"/>
+    </row>
+    <row r="27" spans="1:4" ht="35.25" customHeight="1">
       <c r="A27" s="6"/>
       <c r="B27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="1:4" ht="66" customHeight="1">
+      <c r="A28" s="6"/>
+      <c r="B28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="35.25" customHeight="1">
-      <c r="A28" s="6"/>
-      <c r="B28" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="35.25" customHeight="1">
       <c r="A29" s="6"/>
       <c r="B29" s="9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" s="10"/>
+        <v>34</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="30" spans="1:4" ht="35.25" customHeight="1">
       <c r="A30" s="6"/>
       <c r="B30" s="9" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="63" customHeight="1">
+        <v>37</v>
+      </c>
+      <c r="D30" s="10"/>
+    </row>
+    <row r="31" spans="1:4" ht="35.25" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="9" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="72" customHeight="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="63" customHeight="1">
       <c r="A32" s="6"/>
       <c r="B32" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="72" customHeight="1">
+      <c r="A33" s="6"/>
+      <c r="B33" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C33" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D33" s="10" t="s">
         <v>61</v>
       </c>
+    </row>
+    <row r="34" spans="1:4" ht="31.5">
+      <c r="B34" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="10"/>
+    </row>
+    <row r="35" spans="1:4" ht="31.5">
+      <c r="B35" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C23:D23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
